--- a/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t>#</t>
   </si>
@@ -52,8 +52,12 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Default_Role_1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t>2001</t>
+      <t>Default_Role_</t>
     </r>
     <r>
       <rPr>
@@ -63,112 +67,28 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>,2004,2007</t>
+      <t>2</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Default</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>_Armor_Body</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Armor_Left</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2002,2005,2008</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Armor_Right</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2003,2006,2009</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Body</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2016,2022,2028</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Body_Arm_Left</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2017,2023,2029</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Body_Arm_Right</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2018,2024,2030</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Foot_Left</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2019,2025,2031</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Foot_Right</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2020,2026,2032</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Head</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2021,2027,2033</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Eye_Front_Left</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2055,2056</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2057,2058</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Eye_Back_Left</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Hair</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2046,2047,2048,2049,2050,2051,2052,2053,2054</t>
+    <t>Default_Role_3</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2016,2017,2018,2019,2020,2021,2055,2057,2046,2001</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2022,2023,2024,2025,2026,2027,2055,2057,2048,2004</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>2028,2029,2030,2031,2032,2033,2055,2057,2052,2007</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default_Body，Default_Body_Arm_Left，Default_Body_Arm_Right，Default_Foot_Left，Default_Foot_Right，Default_Head，Default_Eye_Front_Left，Default_Eye_Back_Left，Default_Hair，Armor_Body</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -237,16 +157,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -554,15 +471,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:F17"/>
+  <dimension ref="C2:F8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.75" style="2" customWidth="1"/>
-    <col min="6" max="6" width="38.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="105.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="47.375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -613,148 +530,46 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>9001</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="6" t="s">
+        <v>9013</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
-        <v>9002</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="6" t="s">
-        <v>14</v>
+        <v>9014</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
-        <v>9003</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="6" t="s">
+        <v>9015</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="1">
-        <v>9004</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="1">
-        <v>9005</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="6" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="1">
-        <v>9006</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C12" s="1">
-        <v>9007</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C13" s="1">
-        <v>9008</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C14" s="1">
-        <v>9009</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C15" s="1">
-        <v>9010</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C16" s="1">
-        <v>9011</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C17" s="1">
-        <v>9012</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="6" t="s">
-        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>#</t>
   </si>
@@ -76,19 +76,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>2016,2017,2018,2019,2020,2021,2055,2057,2046,2001</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2022,2023,2024,2025,2026,2027,2055,2057,2048,2004</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2028,2029,2030,2031,2032,2033,2055,2057,2052,2007</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default_Body，Default_Body_Arm_Left，Default_Body_Arm_Right，Default_Foot_Left，Default_Foot_Right，Default_Head，Default_Eye_Front_Left，Default_Eye_Back_Left，Default_Hair，Armor_Body</t>
+    <t>Assets/Bundles/Unit/HeroHuangXiaoYu.prefab</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -478,7 +466,7 @@
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="105.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="47.375" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
@@ -537,9 +525,6 @@
       <c r="D6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="5" t="s">
         <v>14</v>
       </c>
@@ -551,11 +536,8 @@
       <c r="D7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="3:6" x14ac:dyDescent="0.3">
@@ -565,11 +547,8 @@
       <c r="D8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>#</t>
   </si>
@@ -52,31 +52,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Default_Role_1</t>
+    <t>IntValue</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Default_Role_</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Default_Role_3</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Assets/Bundles/Unit/HeroHuangXiaoYu.prefab</t>
+    <t>240</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -459,7 +443,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:F8"/>
+  <dimension ref="C2:G8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -467,16 +451,16 @@
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
     <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="47.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="47.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:7" x14ac:dyDescent="0.3">
       <c r="E2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -489,8 +473,11 @@
       <c r="F3" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>1</v>
       </c>
@@ -503,8 +490,11 @@
       <c r="F4" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>6</v>
       </c>
@@ -517,39 +507,31 @@
       <c r="F5" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="G5" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>9013</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="1">
-        <v>9014</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="1">
-        <v>9015</v>
-      </c>
-      <c r="D8" s="4" t="s">
+        <v>90001</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>14</v>
-      </c>
+    </row>
+    <row r="7" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
+      <c r="D7" s="4"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C8" s="1"/>
+      <c r="D8" s="4"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="28695" windowHeight="13065"/>
   </bookViews>
   <sheets>
-    <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
+    <sheet name="ConstantProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
@@ -80,6 +80,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -87,11 +88,13 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>

--- a/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ConstantConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>#</t>
   </si>
@@ -61,6 +61,30 @@
   </si>
   <si>
     <t>240</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背包格子上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认地图</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0001</t>
+    </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -132,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -143,6 +167,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -453,7 +480,7 @@
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="2" customWidth="1"/>
     <col min="4" max="4" width="21" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="47.375" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="2"/>
   </cols>
@@ -519,16 +546,26 @@
         <v>90001</v>
       </c>
       <c r="D6" s="1"/>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="7" spans="3:7" x14ac:dyDescent="0.3">
-      <c r="C7" s="1"/>
+      <c r="C7" s="1">
+        <v>90002</v>
+      </c>
       <c r="D7" s="4"/>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8" spans="3:7" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
